--- a/data/trans_orig/P36BPD05_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023</t>
+          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117128</t>
+          <t>116076</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185136</t>
+          <t>184546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90840</t>
+          <t>91399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138128</t>
+          <t>135550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227045</t>
+          <t>227018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>308840</t>
+          <t>309204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214851</t>
+          <t>215441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282859</t>
+          <t>283911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174124</t>
+          <t>176702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221412</t>
+          <t>220853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403399</t>
+          <t>403035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485194</t>
+          <t>485221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139661</t>
+          <t>139299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191560</t>
+          <t>192876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173659</t>
+          <t>173554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>333632</t>
+          <t>341146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>333113</t>
+          <t>331899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>520368</t>
+          <t>522527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231987</t>
+          <t>230671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283886</t>
+          <t>284248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177872</t>
+          <t>170358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337845</t>
+          <t>337950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414683</t>
+          <t>412524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601938</t>
+          <t>603152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148806</t>
+          <t>145408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192759</t>
+          <t>191361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144166</t>
+          <t>143356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179871</t>
+          <t>178552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>302857</t>
+          <t>304954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360520</t>
+          <t>360182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343579</t>
+          <t>344977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387532</t>
+          <t>390930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>362597</t>
+          <t>363916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>398302</t>
+          <t>399112</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>718286</t>
+          <t>718624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>775949</t>
+          <t>773852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>244150</t>
+          <t>246965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>695471</t>
+          <t>685898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150888</t>
+          <t>149630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197699</t>
+          <t>196359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>410640</t>
+          <t>413313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1021391</t>
+          <t>982637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191311</t>
+          <t>200884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642632</t>
+          <t>639817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512861</t>
+          <t>514201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>559672</t>
+          <t>560930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>575951</t>
+          <t>614705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1186702</t>
+          <t>1184029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148925</t>
+          <t>149755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188283</t>
+          <t>189350</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115434</t>
+          <t>112756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145519</t>
+          <t>144090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272193</t>
+          <t>273756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>324558</t>
+          <t>321299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369730</t>
+          <t>368663</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409088</t>
+          <t>408258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399238</t>
+          <t>400667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>429323</t>
+          <t>432001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>778212</t>
+          <t>781471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830577</t>
+          <t>829014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94586</t>
+          <t>94012</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122011</t>
+          <t>122523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135519</t>
+          <t>136233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>478697</t>
+          <t>484861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>247513</t>
+          <t>248282</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>702288</t>
+          <t>682623</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243927</t>
+          <t>243415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271352</t>
+          <t>271926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128540</t>
+          <t>122376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>471718</t>
+          <t>471004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270888</t>
+          <t>290553</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>725663</t>
+          <t>724894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89698</t>
+          <t>89356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78490</t>
+          <t>78057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102290</t>
+          <t>102772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150248</t>
+          <t>151473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184538</t>
+          <t>183971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191506</t>
+          <t>191848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215123</t>
+          <t>215396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321599</t>
+          <t>321117</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>345832</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>520555</t>
+          <t>521122</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>554845</t>
+          <t>553620</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1084725</t>
+          <t>1085184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1769508</t>
+          <t>1775515</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1001414</t>
+          <t>1012666</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1635317</t>
+          <t>1655036</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2149513</t>
+          <t>2172576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3110770</t>
+          <t>3117474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1682301</t>
+          <t>1676294</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2367084</t>
+          <t>2366625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2017350</t>
+          <t>1997631</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2651253</t>
+          <t>2640001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3993707</t>
+          <t>3987003</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4954964</t>
+          <t>4931901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD05_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>152782</t>
+          <t>160725</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116076</t>
+          <t>130832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184546</t>
+          <t>193926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>112731</t>
+          <t>130588</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91399</t>
+          <t>106034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135550</t>
+          <t>154662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>265513</t>
+          <t>291313</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227018</t>
+          <t>247723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309204</t>
+          <t>328938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>247205</t>
+          <t>247068</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215441</t>
+          <t>213867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283911</t>
+          <t>276961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>199521</t>
+          <t>230947</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176702</t>
+          <t>206873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220853</t>
+          <t>255501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>446726</t>
+          <t>478015</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403035</t>
+          <t>440390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485221</t>
+          <t>521605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>312252</t>
+          <t>361535</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>312252</t>
+          <t>361535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>312252</t>
+          <t>361535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>712239</t>
+          <t>769328</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>712239</t>
+          <t>769328</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>712239</t>
+          <t>769328</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>163444</t>
+          <t>187239</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139299</t>
+          <t>157726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192876</t>
+          <t>214362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>226292</t>
+          <t>177192</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173554</t>
+          <t>155712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>341146</t>
+          <t>200696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>389736</t>
+          <t>364431</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>331899</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>522527</t>
+          <t>402270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>260103</t>
+          <t>289651</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230671</t>
+          <t>262528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>284248</t>
+          <t>319164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>285212</t>
+          <t>323891</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170358</t>
+          <t>300387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337950</t>
+          <t>345371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>545315</t>
+          <t>613542</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>412524</t>
+          <t>575703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>603152</t>
+          <t>650135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>169964</t>
+          <t>195341</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145408</t>
+          <t>171653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191361</t>
+          <t>222440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>161678</t>
+          <t>185149</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143356</t>
+          <t>165876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178552</t>
+          <t>204999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>331641</t>
+          <t>380491</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304954</t>
+          <t>349281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360182</t>
+          <t>413484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>366374</t>
+          <t>425496</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344977</t>
+          <t>398397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390930</t>
+          <t>449184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>380790</t>
+          <t>436990</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>363916</t>
+          <t>417140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>399112</t>
+          <t>456263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>747165</t>
+          <t>862485</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>718624</t>
+          <t>829492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>773852</t>
+          <t>893695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>431137</t>
+          <t>207172</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>246965</t>
+          <t>183136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>685898</t>
+          <t>232437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>175550</t>
+          <t>195029</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149630</t>
+          <t>175502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>196359</t>
+          <t>214514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>606687</t>
+          <t>402201</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>413313</t>
+          <t>368015</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>982637</t>
+          <t>430963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>455645</t>
+          <t>492511</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200884</t>
+          <t>467246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639817</t>
+          <t>516547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>535010</t>
+          <t>539494</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>514201</t>
+          <t>520009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>560930</t>
+          <t>559021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>990655</t>
+          <t>1032005</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>614705</t>
+          <t>1003243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1184029</t>
+          <t>1066191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>710560</t>
+          <t>734523</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>710560</t>
+          <t>734523</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>710560</t>
+          <t>734523</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1597342</t>
+          <t>1434206</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1597342</t>
+          <t>1434206</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1597342</t>
+          <t>1434206</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>168829</t>
+          <t>181367</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149755</t>
+          <t>159771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189350</t>
+          <t>201919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>129531</t>
+          <t>145946</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112756</t>
+          <t>130689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144090</t>
+          <t>163773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>298360</t>
+          <t>327313</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273756</t>
+          <t>300642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321299</t>
+          <t>355577</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>389184</t>
+          <t>424572</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368663</t>
+          <t>404020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408258</t>
+          <t>446168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>415226</t>
+          <t>459061</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400667</t>
+          <t>441234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>432001</t>
+          <t>474318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>804410</t>
+          <t>883633</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>781471</t>
+          <t>855369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>829014</t>
+          <t>910304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558013</t>
+          <t>605939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558013</t>
+          <t>605939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558013</t>
+          <t>605939</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544757</t>
+          <t>605007</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544757</t>
+          <t>605007</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544757</t>
+          <t>605007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1102770</t>
+          <t>1210946</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1102770</t>
+          <t>1210946</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102770</t>
+          <t>1210946</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,27 +2440,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>107734</t>
+          <t>118673</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94012</t>
+          <t>103235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>135500</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>298868</t>
+          <t>104049</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>136233</t>
+          <t>91350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>484861</t>
+          <t>117917</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>406603</t>
+          <t>222723</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>248282</t>
+          <t>203294</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>682623</t>
+          <t>244273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -2553,22 +2553,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>258204</t>
+          <t>286021</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243415</t>
+          <t>269194</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271926</t>
+          <t>301459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>308369</t>
+          <t>333977</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>122376</t>
+          <t>320109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>471004</t>
+          <t>346676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>566573</t>
+          <t>619997</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>290553</t>
+          <t>598447</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>724894</t>
+          <t>639426</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365938</t>
+          <t>404694</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365938</t>
+          <t>404694</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365938</t>
+          <t>404694</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607237</t>
+          <t>438026</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607237</t>
+          <t>438026</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607237</t>
+          <t>438026</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973176</t>
+          <t>842720</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973176</t>
+          <t>842720</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973176</t>
+          <t>842720</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>77291</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89356</t>
+          <t>99085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>90029</t>
+          <t>99550</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78057</t>
+          <t>87690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102772</t>
+          <t>113457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>167320</t>
+          <t>184979</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>151473</t>
+          <t>165179</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183971</t>
+          <t>203230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>203913</t>
+          <t>223076</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>209420</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215396</t>
+          <t>236149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>333860</t>
+          <t>362960</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321117</t>
+          <t>349053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345832</t>
+          <t>374820</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>537773</t>
+          <t>586036</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>521122</t>
+          <t>567785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>553620</t>
+          <t>605836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281204</t>
+          <t>308505</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281204</t>
+          <t>308505</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281204</t>
+          <t>308505</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423889</t>
+          <t>462510</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423889</t>
+          <t>462510</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423889</t>
+          <t>462510</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705093</t>
+          <t>771015</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705093</t>
+          <t>771015</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705093</t>
+          <t>771015</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1271181</t>
+          <t>1135946</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1085184</t>
+          <t>1071950</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1775515</t>
+          <t>1202254</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1194680</t>
+          <t>1037504</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1012666</t>
+          <t>989836</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1655036</t>
+          <t>1087056</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2465861</t>
+          <t>2173450</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2172576</t>
+          <t>2091863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3117474</t>
+          <t>2250672</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2180628</t>
+          <t>2388395</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1676294</t>
+          <t>2322087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2366625</t>
+          <t>2452391</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2457987</t>
+          <t>2687320</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1997631</t>
+          <t>2637768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2640001</t>
+          <t>2734988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4638616</t>
+          <t>5075715</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3987003</t>
+          <t>4998493</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4931901</t>
+          <t>5157302</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
